--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:15:17+00:00</t>
+    <t>2026-06-15T08:40:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:40:43+00:00</t>
+    <t>2026-06-15T08:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:59:58+00:00</t>
+    <t>2026-06-18T07:59:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T07:59:27+00:00</t>
+    <t>2026-06-18T08:40:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:58+00:00</t>
+    <t>2026-06-18T08:53:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:53:27+00:00</t>
+    <t>2026-06-18T08:56:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:56:30+00:00</t>
+    <t>2026-06-18T10:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T10:39:29+00:00</t>
+    <t>2026-06-18T11:30:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:30:08+00:00</t>
+    <t>2026-06-23T16:45:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T16:45:59+00:00</t>
+    <t>2026-06-24T07:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T07:38:46+00:00</t>
+    <t>2026-06-25T15:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:12:52+00:00</t>
+    <t>2026-07-10T09:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T09:26:12+00:00</t>
+    <t>2026-07-20T12:02:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T12:02:06+00:00</t>
+    <t>2026-07-20T15:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T15:05:40+00:00</t>
+    <t>2026-07-27T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:55:12+00:00</t>
+    <t>2026-07-28T00:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:29:57+00:00</t>
+    <t>2026-07-28T09:41:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T09:41:52+00:00</t>
+    <t>2026-07-29T10:30:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T10:30:12+00:00</t>
+    <t>2026-07-29T11:12:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:12:20+00:00</t>
+    <t>2026-07-29T12:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:36:35+00:00</t>
+    <t>2026-07-30T15:22:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:22:14+00:00</t>
+    <t>2026-07-31T08:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:51:02+00:00</t>
+    <t>2026-07-31T12:16:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codiert die Art eines onkologischen Therapieziels (Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, gemeinsame Entscheidung).</t>
+    <t>Codiert die Art eines onkologischen Therapieziels (Heilung, Lebensverlängerung, Symptomkontrolle, Lebensqualität, Funktionserhalt). Studienteilnahme ist bewusst keine Zielart: Sie ist ein Mittel (investigationale Therapielinie, iLoT nach EnLiST), kein patientenseitiger Zielzustand (vgl. ADR-0015).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -120,7 +120,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>5</t>
   </si>
   <si>
     <t>Level</t>
@@ -181,15 +181,6 @@
   </si>
   <si>
     <t>Erhalt körperlicher oder kognitiver Funktion.</t>
-  </si>
-  <si>
-    <t>studienteilnahme</t>
-  </si>
-  <si>
-    <t>Studienteilnahme</t>
-  </si>
-  <si>
-    <t>Teilnahme an einer klinischen Studie als explizites Ziel.</t>
   </si>
 </sst>
 </file>
@@ -499,7 +490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -586,20 +577,6 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:16:37+00:00</t>
+    <t>2026-07-31T12:21:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -162,7 +162,7 @@
     <t>Symptomkontrolle / Palliation</t>
   </si>
   <si>
-    <t>Linderung von Symptomen und Krankheitslast.</t>
+    <t>Zielzustand einer definierten Symptomlast; symptombezogen erfasst — über Symptomskala oder erfragte Symptomlast.</t>
   </si>
   <si>
     <t>lebensqualitaet</t>
@@ -171,7 +171,7 @@
     <t>Lebensqualität</t>
   </si>
   <si>
-    <t>Erhalt oder Verbesserung von Funktion und Lebensqualität.</t>
+    <t>Erhalt oder Verbesserung der globalen, patientenberichteten Lebensqualität; erfasst per standardisiertem PROM oder strukturiertem Interview (z. B. SEIQoL-DW, Zielklärungsgespräch).</t>
   </si>
   <si>
     <t>funktionserhalt</t>
@@ -180,7 +180,7 @@
     <t>Funktionserhalt</t>
   </si>
   <si>
-    <t>Erhalt körperlicher oder kognitiver Funktion.</t>
+    <t>Erhalt einer konkret benannten Körperfunktion oder -struktur (z. B. Brusterhalt, Kontinenz, Fertilität); patientenpriorisiertes Ziel, das die Maßnahmenwahl in beide Richtungen steuert und eigenständig nachgehalten wird.</t>
   </si>
 </sst>
 </file>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:21:47+00:00</t>
+    <t>2026-07-31T12:58:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:58:15+00:00</t>
+    <t>2026-07-31T13:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:16:40+00:00</t>
+    <t>2026-07-31T13:26:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:26:52+00:00</t>
+    <t>2026-07-31T13:33:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:33:02+00:00</t>
+    <t>2026-07-31T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:38:59+00:00</t>
+    <t>2026-07-31T13:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T13:45:11+00:00</t>
+    <t>2026-07-31T14:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:14:54+00:00</t>
+    <t>2026-07-31T14:25:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:25:45+00:00</t>
+    <t>2026-08-02T18:42:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:42:01+00:00</t>
+    <t>2026-08-02T18:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
+++ b/ci-build/CodeSystem-onko-therapy-goal-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-02T18:51:55+00:00</t>
+    <t>2026-08-03T05:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
